--- a/data/VENTILATION DES SALARIES - COMETE.xlsx
+++ b/data/VENTILATION DES SALARIES - COMETE.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://norix33.sharepoint.com/sites/DATABI/Documents partages/4 - RAMI/VENTILATION DES SALARIES/ventilation-salaries/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2D8703479D696B1026DF3F0CD88FC4CD214AE7A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AB95A78-94B4-41C5-B51F-C13BC97534D8}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2D8703479D696B1026DF3F0CD88FC4CD214AE7A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAE422A3-2EB7-43A0-94E5-7E6D084C4CE0}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="43710" yWindow="4710" windowWidth="14760" windowHeight="5475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28965" yWindow="1455" windowWidth="14760" windowHeight="5475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="comete" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$D$1517</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">comete!$A$1:$D$1517</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26325,6 +26325,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="afd31c10-efa9-482b-aecd-e6150bf66514" xsi:nil="true"/>
@@ -26333,15 +26342,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26364,6 +26364,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9405B9C-7E42-4F85-B2A3-1FFDEC993317}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB43F9E-247A-4BFD-B061-B10CD70C6E9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -26372,12 +26380,4 @@
     <ds:schemaRef ds:uri="3330fc7c-b46e-46a2-bace-63d6ef6932e2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9405B9C-7E42-4F85-B2A3-1FFDEC993317}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>